--- a/pinnacle_league_inputs_web.xlsx
+++ b/pinnacle_league_inputs_web.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AA45CC-41B7-4757-B0CE-9BC26950E863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0811261-CF81-4089-A35B-497032D87DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>LEAGUE</t>
   </si>
@@ -57,6 +57,18 @@
   </si>
   <si>
     <t>Finland - Ykkosliiga</t>
+  </si>
+  <si>
+    <t>FIFA - World Cup</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Brazil - Serie B</t>
   </si>
 </sst>
 </file>
@@ -407,14 +419,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -422,7 +434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -430,7 +442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -438,7 +450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -446,7 +458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -454,7 +466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -462,16 +474,36 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 TLP AMBER (Internal Use)&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 TLP AMBER (Internal Use)</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/pinnacle_league_inputs_web.xlsx
+++ b/pinnacle_league_inputs_web.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0811261-CF81-4089-A35B-497032D87DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42771EED-3C9F-4BF6-9501-EDE43C520511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>LEAGUE</t>
   </si>
@@ -59,16 +59,28 @@
     <t>Finland - Ykkosliiga</t>
   </si>
   <si>
-    <t>FIFA - World Cup</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/fifa-world-cup/matchups/#period:0</t>
-  </si>
-  <si>
     <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/matchups/#period:0</t>
   </si>
   <si>
     <t>Brazil - Serie B</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Poland - Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Poland - 1st Liga</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Romania - Liga 1</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/romania-liga-1/matchups/#period:0</t>
   </si>
 </sst>
 </file>
@@ -419,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
@@ -484,10 +496,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -496,6 +508,22 @@
       </c>
       <c r="B9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
